--- a/recipes/onion-garlic-free-indian/focus-states/05-andhra-pradesh/excel/andhra-pradesh-recipes.xlsx
+++ b/recipes/onion-garlic-free-indian/focus-states/05-andhra-pradesh/excel/andhra-pradesh-recipes.xlsx
@@ -104,7 +104,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="009A3412"/>
-      <sz val="16"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="19">
@@ -259,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -358,6 +358,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="18" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1465,7 +1468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1477,7 +1480,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Bendakaya Vepudu</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Bendakaya Vepudu</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1487,7 +1490,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Andhra Pradesh kitchen  ·  Side  ·  Andhra vegetarian / temple pappu</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Andhra Pradesh  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -1507,44 +1510,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Prep 10 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -1746,37 +1749,203 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="66" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Fry uncovered until the slime goes.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Fry uncovered until the slime goes. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>kcal 71  ·  Protein 3 g  ·  Carbs 9 g  ·  Fat 3 g  ·  Fibre 4 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Sesame · Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="72" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>For Bendakaya Vepudu: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B37" s="52" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="52" t="n"/>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Sesame; Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="31">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -1790,7 +1959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1802,7 +1971,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Cabbage Vepudu</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Cabbage Vepudu</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1812,7 +1981,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Andhra Pradesh kitchen  ·  Side  ·  Andhra vegetarian / temple pappu</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Andhra Pradesh  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -1832,44 +2001,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>12 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>22 min</t>
+          <t>Prep 10 min · Cook 12 min</t>
         </is>
       </c>
     </row>
@@ -2071,37 +2240,203 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="66" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Temper, stir-fry.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Temper, stir-fry. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>kcal 112  ·  Protein 6 g  ·  Carbs 20 g  ·  Fat 2 g  ·  Fibre 6 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="72" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>For Cabbage Vepudu: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B37" s="52" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="52" t="n"/>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="31">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2115,7 +2450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2127,7 +2462,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Dondakaya Fry</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Dondakaya Fry</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2137,7 +2472,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Andhra Pradesh kitchen  ·  Side  ·  Andhra vegetarian / temple pappu</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Andhra Pradesh  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2157,44 +2492,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Prep 10 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -2378,36 +2713,202 @@
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="66" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Fry until the edges catch.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
     </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Fry until the edges catch. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="n"/>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="22" t="n"/>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>kcal 98  ·  Protein 3 g  ·  Carbs 15 g  ·  Fat 3 g  ·  Fibre 2 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B31" s="50" t="n"/>
+      <c r="C31" s="50" t="n"/>
+      <c r="D31" s="50" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="48" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="72" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>For Dondakaya Fry: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B36" s="52" t="n"/>
+      <c r="C36" s="52" t="n"/>
+      <c r="D36" s="52" t="n"/>
+    </row>
+    <row r="37" ht="64" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B37" s="50" t="n"/>
+      <c r="C37" s="50" t="n"/>
+      <c r="D37" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="30">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2421,7 +2922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2433,7 +2934,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Pesarattu</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Pesarattu</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2443,7 +2944,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Andhra Pradesh kitchen  ·  Bread  ·  Andhra vegetarian / temple pappu</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Andhra Pradesh  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2463,44 +2964,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Prep 20 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -2666,35 +3167,188 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="54" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Grind, spread on iron tawa like a dosa.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Cast-iron tawa (not aluminium). Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Grind, spread on iron tawa like a dosa. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: bread is cooked through, no wet dough in the centre, light brown spots on the face.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Hold wrapped in a clean cloth in a covered steel box up to 30 minutes. Refresh on a hot tawa 20 seconds if needed. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>kcal 180  ·  Protein 12 g  ·  Carbs 33 g  ·  Fat 1 g  ·  Fibre 8 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="n"/>
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="50" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>For Pesarattu: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="28">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2708,7 +3362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2720,7 +3374,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Atukulu Upma (breakfast bread)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Atukulu Upma (breakfast bread)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2730,7 +3384,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Andhra Pradesh kitchen  ·  Bread  ·  Andhra vegetarian / temple pappu</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Andhra Pradesh  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2750,44 +3404,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>12 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>22 min</t>
+          <t>Prep 10 min · Cook 12 min</t>
         </is>
       </c>
     </row>
@@ -3025,39 +3679,231 @@
       <c r="C24" s="46" t="n"/>
       <c r="D24" s="46" t="n"/>
     </row>
-    <row r="25" ht="36" customHeight="1">
+    <row r="25" ht="66" customHeight="1">
       <c r="A25" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B25" s="48" t="inlineStr">
         <is>
-          <t>Temper, toss poha. Lemon. No onion.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C25" s="49" t="n"/>
       <c r="D25" s="49" t="n"/>
     </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Temper, toss poha. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="54" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Lemon. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="30" ht="54" customHeight="1">
+      <c r="A30" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>No onion. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B31" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: bread is cooked through, no wet dough in the centre, light brown spots on the face.</t>
+        </is>
+      </c>
+      <c r="C31" s="49" t="n"/>
+      <c r="D31" s="49" t="n"/>
+    </row>
+    <row r="32" ht="42" customHeight="1">
+      <c r="A32" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B32" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C32" s="31" t="n"/>
+      <c r="D32" s="31" t="n"/>
+    </row>
+    <row r="33" ht="42" customHeight="1">
+      <c r="A33" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B33" s="48" t="inlineStr">
+        <is>
+          <t>Hold wrapped in a clean cloth in a covered steel box up to 30 minutes. Refresh on a hot tawa 20 seconds if needed. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C33" s="49" t="n"/>
+      <c r="D33" s="49" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="n"/>
+      <c r="C35" s="22" t="n"/>
+      <c r="D35" s="22" t="n"/>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>kcal 223  ·  Protein 6 g  ·  Carbs 41 g  ·  Fat 4 g  ·  Fibre 3 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+    </row>
+    <row r="38" ht="48" customHeight="1">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="n"/>
+      <c r="C38" s="26" t="n"/>
+      <c r="D38" s="26" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n"/>
+    </row>
+    <row r="40" ht="72" customHeight="1">
+      <c r="A40" s="25" t="inlineStr">
+        <is>
+          <t>For Atukulu Upma (breakfast bread): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B40" s="26" t="n"/>
+      <c r="C40" s="26" t="n"/>
+      <c r="D40" s="26" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B41" s="52" t="n"/>
+      <c r="C41" s="52" t="n"/>
+      <c r="D41" s="52" t="n"/>
+    </row>
+    <row r="42" ht="64" customHeight="1">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B42" s="50" t="n"/>
+      <c r="C42" s="50" t="n"/>
+      <c r="D42" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="35">
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
     <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
     <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B28:D28"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A40:D40"/>
     <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B33:D33"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C21:D21"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="A41:D41"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A42:D42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3071,7 +3917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3083,7 +3929,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Jonna Rotte</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Jonna Rotte</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3093,7 +3939,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Andhra Pradesh kitchen  ·  Bread  ·  Andhra vegetarian / temple pappu</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Andhra Pradesh  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3113,44 +3959,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 15 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -3280,33 +4126,186 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="54" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Pat and cook on iron tawa.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Cast-iron tawa (not aluminium). Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
       <c r="D19" s="49" t="n"/>
     </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Pat and cook on iron tawa. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: bread is cooked through, no wet dough in the centre, light brown spots on the face.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Hold wrapped in a clean cloth in a covered steel box up to 30 minutes. Refresh on a hot tawa 20 seconds if needed. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>kcal 75  ·  Protein 2 g  ·  Carbs 11 g  ·  Fat 2 g  ·  Fibre 2 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B27" s="50" t="n"/>
+      <c r="C27" s="50" t="n"/>
+      <c r="D27" s="50" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="72" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>For Jonna Rotte: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B32" s="52" t="n"/>
+      <c r="C32" s="52" t="n"/>
+      <c r="D32" s="52" t="n"/>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="26">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3320,7 +4319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3332,7 +4331,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Ariselu</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Ariselu</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3342,7 +4341,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Andhra Pradesh kitchen  ·  Sweet  ·  Andhra vegetarian / temple pappu</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Andhra Pradesh  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3362,44 +4361,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>65 min</t>
+          <t>Prep 40 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -3547,34 +4546,187 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="66" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Pat discs, fry in ghee.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel kadhai for frying — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Pat discs, fry in ghee. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 424  ·  Protein 4 g  ·  Carbs 80 g  ·  Fat 10 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Sesame · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Ariselu: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Milk; Sesame; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="27">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3588,7 +4740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3600,7 +4752,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Bobbatlu</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Bobbatlu</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3610,7 +4762,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Andhra Pradesh kitchen  ·  Sweet  ·  Andhra vegetarian / temple pappu</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Andhra Pradesh  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3630,44 +4782,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>65 min</t>
+          <t>Prep 40 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -3779,32 +4931,185 @@
       <c r="C17" s="46" t="n"/>
       <c r="D17" s="46" t="n"/>
     </row>
-    <row r="18" ht="36" customHeight="1">
+    <row r="18" ht="54" customHeight="1">
       <c r="A18" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B18" s="48" t="inlineStr">
         <is>
-          <t>Stuff, roll, cook on iron with ghee.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Cast-iron tawa (not aluminium). Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C18" s="49" t="n"/>
       <c r="D18" s="49" t="n"/>
     </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="31" t="n"/>
+    </row>
+    <row r="20" ht="54" customHeight="1">
+      <c r="A20" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="48" t="inlineStr">
+        <is>
+          <t>Stuff, roll, cook on iron with ghee. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C20" s="49" t="n"/>
+      <c r="D20" s="49" t="n"/>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="n"/>
+      <c r="C25" s="22" t="n"/>
+      <c r="D25" s="22" t="n"/>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>kcal 452  ·  Protein 18 g  ·  Carbs 86 g  ·  Fat 4 g  ·  Fibre 12 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B26" s="50" t="n"/>
+      <c r="C26" s="50" t="n"/>
+      <c r="D26" s="50" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="n"/>
+      <c r="C28" s="26" t="n"/>
+      <c r="D28" s="26" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="72" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>For Bobbatlu: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B31" s="52" t="n"/>
+      <c r="C31" s="52" t="n"/>
+      <c r="D31" s="52" t="n"/>
+    </row>
+    <row r="32" ht="64" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="25">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3818,7 +5123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3830,7 +5135,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Rava Laddu</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Rava Laddu</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3840,7 +5145,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Andhra Pradesh kitchen  ·  Sweet  ·  Andhra vegetarian / temple pappu</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Andhra Pradesh  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3860,44 +5165,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 15 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -4063,35 +5368,188 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="66" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Mix, shape ladoos.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. Use a heavy stainless steel milk pot. Acidic or milk dishes must never touch aluminium.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Mix, shape ladoos. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>kcal 622  ·  Protein 9 g  ·  Carbs 39 g  ·  Fat 49 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="n"/>
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="50" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>For Rava Laddu: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="28">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4105,7 +5563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4117,7 +5575,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Paramannam</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Paramannam</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4127,7 +5585,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Andhra Pradesh kitchen  ·  Dessert  ·  Andhra vegetarian / temple pappu</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Andhra Pradesh  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4147,44 +5605,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Prep 10 min · Cook 35 min</t>
         </is>
       </c>
     </row>
@@ -4350,35 +5808,188 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="66" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Temple rice pudding in steel.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Heavy stainless steel milk pot — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. Use a heavy stainless steel milk pot. Acidic or milk dishes must never touch aluminium.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Temple rice pudding in steel. Work in Heavy stainless steel milk pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>kcal 464  ·  Protein 13 g  ·  Carbs 78 g  ·  Fat 12 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="n"/>
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="50" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>For Paramannam: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Serve in steel or glass bowls. If chilled, take out 5 minutes before the pass. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="28">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4656,7 +6267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4668,7 +6279,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Rava Kesari</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Rava Kesari</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4678,7 +6289,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Andhra Pradesh kitchen  ·  Dessert  ·  Andhra vegetarian / temple pappu</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Andhra Pradesh  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4698,44 +6309,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Prep 10 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -4919,36 +6530,189 @@
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="66" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Roast rava in ghee, add water, sugar, saffron.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
     </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Roast rava in ghee, add water, sugar, saffron. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 233  ·  Protein 2 g  ·  Carbs 33 g  ·  Fat 11 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Rava Kesari: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Serve in steel or glass bowls. If chilled, take out 5 minutes before the pass. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="29">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4962,7 +6726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4974,7 +6738,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Semiya Payasam</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Semiya Payasam</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4984,7 +6748,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Andhra Pradesh kitchen  ·  Dessert  ·  Andhra vegetarian / temple pappu</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Andhra Pradesh  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -5004,44 +6768,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot or chilled</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Prep 5 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -5207,35 +6971,188 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="66" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Cook in steel.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Heavy stainless steel milk pot — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. Use a heavy stainless steel milk pot. Acidic or milk dishes must never touch aluminium.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Cook in steel. Work in Heavy stainless steel milk pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot or chilled.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>kcal 309  ·  Protein 10 g  ·  Carbs 43 g  ·  Fat 12 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="n"/>
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="50" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>For Semiya Payasam: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Serve in steel or glass bowls. If chilled, take out 5 minutes before the pass. Service temperature: Hot or chilled. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="28">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5249,7 +7166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5261,7 +7178,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Tomato Pachadi</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Tomato Pachadi</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5271,7 +7188,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Andhra Pradesh kitchen  ·  Salad  ·  Andhra vegetarian / temple pappu</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Andhra Pradesh  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -5291,44 +7208,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Prep 10 min · Cook 5 min</t>
         </is>
       </c>
     </row>
@@ -5512,36 +7429,202 @@
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="54" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Crush, temper.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
     </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Steel or glass bowl on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Crush, temper. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables stay crisp; dressing coats evenly; seasoning is bright, not flat.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Cold.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="n"/>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="22" t="n"/>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>kcal 14  ·  Protein 1 g  ·  Carbs 3 g  ·  Fat 0 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B31" s="50" t="n"/>
+      <c r="C31" s="50" t="n"/>
+      <c r="D31" s="50" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="48" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="72" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>For Tomato Pachadi: squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B36" s="52" t="n"/>
+      <c r="C36" s="52" t="n"/>
+      <c r="D36" s="52" t="n"/>
+    </row>
+    <row r="37" ht="64" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Dress at the last minute. Toss at the pass, do not send a wet bowl. Service temperature: Cold. Allergen label for this dish: Gluten (wheat); Milk; Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B37" s="50" t="n"/>
+      <c r="C37" s="50" t="n"/>
+      <c r="D37" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="30">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5555,7 +7638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5567,7 +7650,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Menthi Pachadi</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Menthi Pachadi</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5577,7 +7660,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Andhra Pradesh kitchen  ·  Salad  ·  Andhra vegetarian / temple pappu</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Andhra Pradesh  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -5597,44 +7680,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Prep 15 min · Cook 10 min</t>
         </is>
       </c>
     </row>
@@ -5800,35 +7883,201 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="66" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Grind, mix. A little goes a long way.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Grind, mix. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>A little goes a long way. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables stay crisp; dressing coats evenly; seasoning is bright, not flat.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Cold.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 7  ·  Protein 0 g  ·  Carbs 1 g  ·  Fat 0 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Menthi Pachadi: squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Dress at the last minute. Toss at the pass, do not send a wet bowl. Service temperature: Cold. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="29">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5842,7 +8091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5854,7 +8103,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Cabbage Pachadi</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Cabbage Pachadi</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5864,7 +8113,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Andhra Pradesh kitchen  ·  Salad  ·  Andhra vegetarian / temple pappu</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Andhra Pradesh  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -5884,44 +8133,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>8 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>18 min</t>
+          <t>Prep 10 min · Cook 8 min</t>
         </is>
       </c>
     </row>
@@ -6105,36 +8354,202 @@
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="66" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Quick stir, temper, optional yogurt.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
     </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Quick stir, temper, optional yogurt. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables stay crisp; dressing coats evenly; seasoning is bright, not flat.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Cold.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="n"/>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="22" t="n"/>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>kcal 37  ·  Protein 2 g  ·  Carbs 6 g  ·  Fat 1 g  ·  Fibre 2 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B31" s="50" t="n"/>
+      <c r="C31" s="50" t="n"/>
+      <c r="D31" s="50" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="48" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="72" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>For Cabbage Pachadi: squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B36" s="52" t="n"/>
+      <c r="C36" s="52" t="n"/>
+      <c r="D36" s="52" t="n"/>
+    </row>
+    <row r="37" ht="64" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Dress at the last minute. Toss at the pass, do not send a wet bowl. Service temperature: Cold. Allergen label for this dish: Gluten (wheat); Milk; Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B37" s="50" t="n"/>
+      <c r="C37" s="50" t="n"/>
+      <c r="D37" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="30">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -9670,7 +12085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9682,7 +12097,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Punugulu</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Punugulu</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9692,7 +12107,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Andhra Pradesh kitchen  ·  Starter  ·  Andhra vegetarian / temple pappu</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Andhra Pradesh  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -9712,44 +12127,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 15 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -9933,36 +12348,202 @@
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="66" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Fry small blobs in steel.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel kadhai for frying — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
     </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Steel kadhai for frying — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Fry small blobs in steel. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: crust or crumb is set, centre is hot, no raw flour or potato taste. Drain on a steel rack, not paper in the fryer basket.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="n"/>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="22" t="n"/>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>kcal 261  ·  Protein 7 g  ·  Carbs 30 g  ·  Fat 14 g  ·  Fibre 5 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B31" s="50" t="n"/>
+      <c r="C31" s="50" t="n"/>
+      <c r="D31" s="50" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="48" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="72" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>For Punugulu: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B36" s="52" t="n"/>
+      <c r="C36" s="52" t="n"/>
+      <c r="D36" s="52" t="n"/>
+    </row>
+    <row r="37" ht="64" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B37" s="50" t="n"/>
+      <c r="C37" s="50" t="n"/>
+      <c r="D37" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="30">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -9976,7 +12557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9988,7 +12569,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Garelu (Minapa Vada)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Garelu (Minapa Vada)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9998,7 +12579,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Andhra Pradesh kitchen  ·  Starter  ·  Andhra vegetarian / temple pappu</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Andhra Pradesh  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -10018,44 +12599,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Prep 20 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -10257,37 +12838,203 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="66" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Grind, shape rings, fry.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel kadhai for frying — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Steel kadhai for frying — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Grind, shape rings, fry. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: crust or crumb is set, centre is hot, no raw flour or potato taste. Drain on a steel rack, not paper in the fryer basket.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>kcal 111  ·  Protein 3 g  ·  Carbs 9 g  ·  Fat 7 g  ·  Fibre 2 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="72" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>For Garelu (Minapa Vada): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B37" s="52" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="52" t="n"/>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="31">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -10301,7 +13048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10313,7 +13060,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Perugu Vada</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Perugu Vada</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10323,7 +13070,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Andhra Pradesh kitchen  ·  Starter  ·  Andhra vegetarian / temple pappu</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Andhra Pradesh  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -10343,44 +13090,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 20 min · Cook 10 min</t>
         </is>
       </c>
     </row>
@@ -10564,36 +13311,202 @@
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="54" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Soak vadas, pour tempered yogurt.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
     </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Steel or glass bowl on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Soak vadas, pour tempered yogurt. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: crust or crumb is set, centre is hot, no raw flour or potato taste. Drain on a steel rack, not paper in the fryer basket.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="n"/>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="22" t="n"/>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>kcal 226  ·  Protein 8 g  ·  Carbs 32 g  ·  Fat 8 g  ·  Fibre 5 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B31" s="50" t="n"/>
+      <c r="C31" s="50" t="n"/>
+      <c r="D31" s="50" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="48" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="72" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>For Perugu Vada: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder. Bring yogurt to a simmer gently and stir; a rolling boil can split it.</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B36" s="52" t="n"/>
+      <c r="C36" s="52" t="n"/>
+      <c r="D36" s="52" t="n"/>
+    </row>
+    <row r="37" ht="64" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B37" s="50" t="n"/>
+      <c r="C37" s="50" t="n"/>
+      <c r="D37" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="30">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -10607,7 +13520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10619,7 +13532,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Gongura Pappu</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Gongura Pappu</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10629,7 +13542,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Andhra Pradesh kitchen  ·  Main  ·  Andhra vegetarian / temple pappu</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Andhra Pradesh  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -10649,44 +13562,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Prep 10 min · Cook 30 min</t>
         </is>
       </c>
     </row>
@@ -10906,38 +13819,243 @@
       <c r="C23" s="46" t="n"/>
       <c r="D23" s="46" t="n"/>
     </row>
-    <row r="24" ht="36" customHeight="1">
+    <row r="24" ht="66" customHeight="1">
       <c r="A24" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B24" s="48" t="inlineStr">
         <is>
-          <t>Cook dal. Wilt gongura in tadka. Mix. No onion.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel or clay pot — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C24" s="49" t="n"/>
       <c r="D24" s="49" t="n"/>
     </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel or clay pot — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Cook dal. Work in Stainless steel or clay pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Wilt gongura in tadka. Work in Stainless steel or clay pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="29" ht="54" customHeight="1">
+      <c r="A29" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>Mix. Work in Stainless steel or clay pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="31" t="n"/>
+    </row>
+    <row r="30" ht="54" customHeight="1">
+      <c r="A30" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B30" s="48" t="inlineStr">
+        <is>
+          <t>No onion. Work in Stainless steel or clay pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C31" s="31" t="n"/>
+      <c r="D31" s="31" t="n"/>
+    </row>
+    <row r="32" ht="42" customHeight="1">
+      <c r="A32" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B32" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C32" s="49" t="n"/>
+      <c r="D32" s="49" t="n"/>
+    </row>
+    <row r="33" ht="42" customHeight="1">
+      <c r="A33" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="B33" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C33" s="31" t="n"/>
+      <c r="D33" s="31" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="n"/>
+      <c r="C35" s="22" t="n"/>
+      <c r="D35" s="22" t="n"/>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>kcal 179  ·  Protein 10 g  ·  Carbs 31 g  ·  Fat 2 g  ·  Fibre 7 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+    </row>
+    <row r="38" ht="48" customHeight="1">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="n"/>
+      <c r="C38" s="26" t="n"/>
+      <c r="D38" s="26" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n"/>
+    </row>
+    <row r="40" ht="72" customHeight="1">
+      <c r="A40" s="25" t="inlineStr">
+        <is>
+          <t>For Gongura Pappu: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B40" s="26" t="n"/>
+      <c r="C40" s="26" t="n"/>
+      <c r="D40" s="26" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B41" s="52" t="n"/>
+      <c r="C41" s="52" t="n"/>
+      <c r="D41" s="52" t="n"/>
+    </row>
+    <row r="42" ht="64" customHeight="1">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B42" s="50" t="n"/>
+      <c r="C42" s="50" t="n"/>
+      <c r="D42" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="C20:D20"/>
+  <mergeCells count="35">
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
-    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A42:D42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -10951,7 +14069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10963,7 +14081,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Tomato Pappu</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Tomato Pappu</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10973,7 +14091,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Andhra Pradesh kitchen  ·  Main  ·  Andhra vegetarian / temple pappu</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Andhra Pradesh  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -10993,44 +14111,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Prep 10 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -11250,38 +14368,217 @@
       <c r="C23" s="46" t="n"/>
       <c r="D23" s="46" t="n"/>
     </row>
-    <row r="24" ht="36" customHeight="1">
+    <row r="24" ht="66" customHeight="1">
       <c r="A24" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B24" s="48" t="inlineStr">
         <is>
-          <t>Cook dal with tomato. Temper.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel or clay pot — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C24" s="49" t="n"/>
       <c r="D24" s="49" t="n"/>
     </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel or clay pot — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Cook dal with tomato. Work in Stainless steel or clay pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Temper. Work in Stainless steel or clay pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="31" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B30" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C31" s="31" t="n"/>
+      <c r="D31" s="31" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="n"/>
+      <c r="C33" s="22" t="n"/>
+      <c r="D33" s="22" t="n"/>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>kcal 147  ·  Protein 9 g  ·  Carbs 28 g  ·  Fat 1 g  ·  Fibre 7 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="48" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+    </row>
+    <row r="38" ht="72" customHeight="1">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>For Tomato Pappu: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="n"/>
+      <c r="C38" s="26" t="n"/>
+      <c r="D38" s="26" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B39" s="52" t="n"/>
+      <c r="C39" s="52" t="n"/>
+      <c r="D39" s="52" t="n"/>
+    </row>
+    <row r="40" ht="64" customHeight="1">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B40" s="50" t="n"/>
+      <c r="C40" s="50" t="n"/>
+      <c r="D40" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="C20:D20"/>
+  <mergeCells count="33">
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
-    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A33:D33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -11295,7 +14592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11307,7 +14604,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Pulihora</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Pulihora</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11317,7 +14614,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Andhra Pradesh kitchen  ·  Main  ·  Andhra vegetarian / temple pappu</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Andhra Pradesh  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -11337,44 +14634,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Prep 15 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -11648,41 +14945,233 @@
       <c r="C26" s="46" t="n"/>
       <c r="D26" s="46" t="n"/>
     </row>
-    <row r="27" ht="42" customHeight="1">
+    <row r="27" ht="66" customHeight="1">
       <c r="A27" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B27" s="48" t="inlineStr">
         <is>
-          <t>Cook tamarind with spices until thick. Mix into rice. Temple food — no allium.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C27" s="49" t="n"/>
       <c r="D27" s="49" t="n"/>
     </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="54" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="30" ht="54" customHeight="1">
+      <c r="A30" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>Cook tamarind with spices until thick. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+    </row>
+    <row r="31" ht="54" customHeight="1">
+      <c r="A31" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B31" s="48" t="inlineStr">
+        <is>
+          <t>Mix into rice. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C31" s="49" t="n"/>
+      <c r="D31" s="49" t="n"/>
+    </row>
+    <row r="32" ht="54" customHeight="1">
+      <c r="A32" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B32" s="30" t="inlineStr">
+        <is>
+          <t>Temple food — no allium. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C32" s="31" t="n"/>
+      <c r="D32" s="31" t="n"/>
+    </row>
+    <row r="33" ht="42" customHeight="1">
+      <c r="A33" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B33" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C33" s="49" t="n"/>
+      <c r="D33" s="49" t="n"/>
+    </row>
+    <row r="34" ht="42" customHeight="1">
+      <c r="A34" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B34" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C34" s="31" t="n"/>
+      <c r="D34" s="31" t="n"/>
+    </row>
+    <row r="35" ht="42" customHeight="1">
+      <c r="A35" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B35" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C35" s="49" t="n"/>
+      <c r="D35" s="49" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B37" s="22" t="n"/>
+      <c r="C37" s="22" t="n"/>
+      <c r="D37" s="22" t="n"/>
+    </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>kcal 546  ·  Protein 17 g  ·  Carbs 105 g  ·  Fat 6 g  ·  Fibre 9 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n"/>
+    </row>
+    <row r="40" ht="48" customHeight="1">
+      <c r="A40" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B40" s="26" t="n"/>
+      <c r="C40" s="26" t="n"/>
+      <c r="D40" s="26" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="n"/>
+      <c r="C41" s="6" t="n"/>
+      <c r="D41" s="6" t="n"/>
+    </row>
+    <row r="42" ht="72" customHeight="1">
+      <c r="A42" s="25" t="inlineStr">
+        <is>
+          <t>For Pulihora: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B42" s="26" t="n"/>
+      <c r="C42" s="26" t="n"/>
+      <c r="D42" s="26" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B43" s="52" t="n"/>
+      <c r="C43" s="52" t="n"/>
+      <c r="D43" s="52" t="n"/>
+    </row>
+    <row r="44" ht="64" customHeight="1">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B44" s="50" t="n"/>
+      <c r="C44" s="50" t="n"/>
+      <c r="D44" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="37">
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A38:D38"/>
     <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="A44:D44"/>
     <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B28:D28"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A40:D40"/>
     <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A39:D39"/>
     <mergeCell ref="C22:D22"/>
+    <mergeCell ref="B30:D30"/>
     <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B33:D33"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C21:D21"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B35:D35"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A41:D41"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="C23:D23"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A42:D42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
